--- a/sheets/조재수대금교본/검수/서편제 OST.xlsx
+++ b/sheets/조재수대금교본/검수/서편제 OST.xlsx
@@ -3087,16 +3087,11 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
@@ -3109,7 +3104,6 @@
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-ﾉ
 –㑲</t>
         </is>
       </c>
@@ -3195,48 +3189,23 @@
     </row>
     <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
     </row>
     <row r="9" ht="96.05" customHeight="true">
@@ -3262,7 +3231,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -3337,49 +3306,41 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∼
-‹</t>
+          <t xml:space="preserve">姑∼</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c㴌潢
-–ﾉ</t>
+          <t xml:space="preserve">㴌潢
+–</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∼
-‹</t>
+          <t xml:space="preserve">姑∼</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c㴌潢
-–ﾉ</t>
+          <t xml:space="preserve">㴌潢
+–</t>
         </is>
       </c>
       <c r="I11" s="24"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J11" s="21"/>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∼
-‹</t>
+          <t xml:space="preserve">姑∼</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-ﾉ
 –㑲</t>
         </is>
       </c>
@@ -3403,7 +3364,7 @@
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林潢
-南∽</t>
+南</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3415,15 +3376,14 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林潢
-南∽</t>
+南</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -3463,41 +3423,17 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/서편제 OST.xlsx
+++ b/sheets/조재수대금교본/검수/서편제 OST.xlsx
@@ -3104,6 +3104,7 @@
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
+ﾉ
 –㑲</t>
         </is>
       </c>
@@ -3231,7 +3232,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -3312,8 +3313,8 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌潢
-–</t>
+          <t xml:space="preserve">c㴌潢
+–ﾉ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -3325,8 +3326,8 @@
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌潢
-–</t>
+          <t xml:space="preserve">c㴌潢
+–ﾉ</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -3341,6 +3342,7 @@
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
+ﾉ
 –㑲</t>
         </is>
       </c>
@@ -3364,7 +3366,7 @@
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林潢
-南</t>
+南∽</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3376,14 +3378,15 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林潢
-南</t>
+南∽</t>
         </is>
       </c>
       <c r="M12" s="22"/>

--- a/sheets/조재수대금교본/검수/서편제 OST.xlsx
+++ b/sheets/조재수대금교본/검수/서편제 OST.xlsx
@@ -2950,26 +2950,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="65.57" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="97.63" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="97.63" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3065,7 +3065,7 @@
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="97.63" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="97.63" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="97.63" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -3188,7 +3188,7 @@
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="97.63" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -3209,7 +3209,7 @@
       <c r="N8" s="21"/>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="97.63" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="97.63" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="97.63" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="97.63" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="97.63" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3418,7 +3418,7 @@
       <c r="N13" s="21"/>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="97.63" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3445,6 +3445,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
 </worksheet>
 </file>